--- a/docs/v3.0.0-preview1/ValueSet-VRM-DemographicsCodingHeaderURI-vs.xlsx
+++ b/docs/v3.0.0-preview1/ValueSet-VRM-DemographicsCodingHeaderURI-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-09T11:35:05-04:00</t>
+    <t>2025-08-11T15:01:09-04:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/v3.0.0-preview1/ValueSet-VRM-DemographicsCodingHeaderURI-vs.xlsx
+++ b/docs/v3.0.0-preview1/ValueSet-VRM-DemographicsCodingHeaderURI-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-08-11T15:01:09-04:00</t>
+    <t>2025-11-25T14:04:25-05:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/v3.0.0-preview1/ValueSet-VRM-DemographicsCodingHeaderURI-vs.xlsx
+++ b/docs/v3.0.0-preview1/ValueSet-VRM-DemographicsCodingHeaderURI-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-11-25T14:04:25-05:00</t>
+    <t>2026-03-24T12:23:49-04:00</t>
   </si>
   <si>
     <t>Publisher</t>
